--- a/important_mails_2026-04-30.xlsx
+++ b/important_mails_2026-04-30.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H152"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
+          <t>Thu, 30 Apr 2026 14:14:16 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -510,11 +510,301 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:03:36 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Add products to Amazon.nl for Pan EU eligibility</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Add products to Amazon.nl for Pan EU eligibility 96
+ Complete Pan EU enrollment: Add NL products now
+                                                     ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
+ Complete Pan EU enrollment: Add NL products now
+ Add an of</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 09:05:17 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>【请勿回复此日志，如有问题请加入下方邮件中的企微群】
+卖家您好，
+系统数据显示您可能在以下站点尚未完成PPWR合规。提醒您务必尽快开始行动。如果您被认定为不合规，根据国家/地区不同，亚马逊可能需要停售您的不合规商品。
+【您需要完成的事项】
+1. 完成 IT, ES, NL, BE, PL, SE, IE 站点的包装法号码注册和上传。上传路径：绩效 → 账户状况 → 监管合规性 → 点击右上角【提交合规信息】→ 选择“EPR合规-包装“ → 上传号码。
+2. 西班牙包装法注册需要西班牙本地税号，您目前可能尚未持有。请立刻开始注册流程，以确保在法规生效日（8月12日）前完成合规。
+【资源链接】
+- 服务商网络PPWR专属页面：https://spn.globalsellingcommunity.cn/dynamicMarketingLanding?id=16&amp;launchPositionCode=5PCR95
+- PPWR合规操作手册：https://m.media-amazon.com/images/G/01/CN_Compliance_Team/PPWR_Compliance_Guidebook.pdf
+【问卷调查及问题反馈】
+我们想了解下您当前在PPWR的合规进度以及收集您遇到的问题，还请填写下列问卷，谢谢：https://suv.ma.globalsellingcommunity.cn/t/5RRVUV
+如有疑问，请扫码加入亚马逊卖家合规群：
+https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
+To contact us again about this issue, please use the Contact Us form in Seller Central using the following link:
+https://sellercentral-europe.amazon.com/cu/case-dashboard/view-case?caseID=12309992722
+Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Pagamento elaborato con successo</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
+ Tentativo di pagamento
+Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
+In data 04/30/26 14:07 CEST, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
+ 215,29.
+ Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
+ Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
+ Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
+Befristetes Angebot -15 % 20,36 € Statt: 23,95 €
+https://www.amazon.de/gp/product/B0DRCB74YN/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+75x120 cm Feuerfeste Unterlage, Hitzeschutzmatte, Antihaft-Material Bodenschutzmatte, Grill Matten, Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ 19,99 €
+https://www.amazon.de/gp/product/B0DBLM41YS/?ref_=ci_mcx_mr_2p_0_lm
+100 * 150cm Feuerfeste Unterlage - Hitzebeständig bis 1800°F Hitzeschutzmatte - Grillteppich Bodenschutzmatte Grillmatten Bodenmatte Feuerstellenmatte Outdoor BBQ Matte für Gasgrill Holzkohlegrill
+ -17 % 29,98 € UVP: 35,99 €
+https://www.amazon.de/gp/product/B0BRTPDYMV/?ref_=ci_mcx_mr_2p_1_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+Befristetes Angebot -18 % 20,38 € UVP: 24,</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -534,39 +824,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -583,39 +873,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -635,39 +925,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -681,91 +971,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 04/23/26 15:01 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 159.20.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -781,39 +1019,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -832,39 +1070,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -875,39 +1113,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -926,39 +1164,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -977,39 +1215,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -1028,39 +1266,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -1089,40 +1327,40 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -1135,39 +1373,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -1182,39 +1420,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -1227,40 +1465,40 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -1275,40 +1513,40 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -1322,39 +1560,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -1368,39 +1606,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -1415,39 +1653,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -1461,39 +1699,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -1508,39 +1746,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1555,39 +1793,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1606,39 +1844,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1654,39 +1892,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1707,39 +1945,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -1757,40 +1995,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -1808,39 +2046,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1857,39 +2095,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -1907,40 +2145,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1958,39 +2196,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -2008,39 +2246,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2064,39 +2302,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2117,39 +2355,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -2198,39 +2436,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2246,39 +2484,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2298,39 +2536,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2356,39 +2594,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2409,39 +2647,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2467,39 +2705,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2519,39 +2757,91 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 04/23/26 15:01 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 159.20.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2568,39 +2858,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2616,39 +2906,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2668,39 +2958,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2717,39 +3007,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -2761,39 +3051,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2816,39 +3106,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2872,39 +3162,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -2919,39 +3209,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2965,40 +3255,40 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3015,39 +3305,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3067,39 +3357,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3116,39 +3406,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3171,39 +3461,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3223,39 +3513,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -3284,39 +3574,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3334,39 +3624,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3384,39 +3674,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3434,39 +3724,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -3480,39 +3770,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3530,40 +3820,40 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3580,40 +3870,40 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3630,39 +3920,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -3696,39 +3986,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3743,39 +4033,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3791,39 +4081,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -3847,39 +4137,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3898,39 +4188,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -3946,39 +4236,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -3990,39 +4280,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4042,39 +4332,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4092,40 +4382,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4143,39 +4433,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -4195,39 +4485,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4248,39 +4538,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4301,40 +4591,40 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -4350,39 +4640,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -4405,39 +4695,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4455,39 +4745,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4505,39 +4795,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -4557,39 +4847,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4606,39 +4896,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4653,39 +4943,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4704,39 +4994,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -4754,39 +5044,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -4825,39 +5115,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4873,40 +5163,40 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4922,39 +5212,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4970,39 +5260,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5016,40 +5306,40 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5065,39 +5355,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5113,39 +5403,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5166,39 +5456,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5213,39 +5503,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -5262,39 +5552,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5308,39 +5598,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -5359,40 +5649,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -5406,40 +5696,40 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -5457,39 +5747,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -5522,39 +5812,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -5569,39 +5859,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5620,39 +5910,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -5671,39 +5961,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -5715,39 +6005,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -5763,39 +6053,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -5807,39 +6097,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5854,39 +6144,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5898,39 +6188,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5942,39 +6232,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5986,39 +6276,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6030,39 +6320,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6074,39 +6364,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6118,39 +6408,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6162,39 +6452,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6206,39 +6496,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6250,39 +6540,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6301,39 +6591,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6345,39 +6635,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6389,39 +6679,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6433,39 +6723,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6477,39 +6767,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6521,39 +6811,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6565,39 +6855,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6609,39 +6899,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6660,39 +6950,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6704,40 +6994,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6756,39 +7046,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6800,39 +7090,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6851,39 +7141,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -6915,39 +7205,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -6974,39 +7264,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -7018,39 +7308,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -7060,39 +7350,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -7102,39 +7392,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -7164,39 +7454,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7214,39 +7504,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7263,39 +7553,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -7311,39 +7601,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -7372,39 +7662,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7426,39 +7716,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7481,39 +7771,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7534,39 +7824,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7589,39 +7879,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -7634,39 +7924,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -7675,39 +7965,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7723,39 +8013,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -7771,39 +8061,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7823,39 +8113,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7874,39 +8164,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7915,39 +8205,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7965,39 +8255,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026

--- a/important_mails_2026-04-30.xlsx
+++ b/important_mails_2026-04-30.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -645,21 +645,179 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
+          <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+          <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>立即规划您的促销
+尊敬的卖家：
+通过为您选定的商品提报Z划算和促销（价格折扣和优惠券），为亚马逊 La French Week 做好准备。
+请为您的产品提报活动期间的促销。
+关键日期
+活动日期： 2026年4月29日至5月5日
+Z划算提报截止日期： 开始日期前1天
+优惠券和价格折扣提报截止日期： 活动结束前 12 小时
+即刻提报您的促销活动 &gt; https://go.amazonsellerservices.com/e/229492/-ld-DC-EM-D440543605-Wk18/7z351dt/6634643451/h/aAlToMVZuL9Pf26IUgl4EwypMRINffcPORYtB0qJpQs
+您的 ASIN 推荐清单
+以下为您精选推荐的 ASIN，可用于提交至 La French Week。
+&lt;div style="padding: 0 20px; "&gt;&lt;table style="width:100%; border-collapse:collapse; text-align:center; font-family:Amazon Ember Display, Arial, sans-serif; border:2px solid #868D95; border-radius:10px 10px 0 0; overflow:hidden; "&gt;&lt;thead&gt;&lt;tr style="background-color:#dfdad5;"&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;站点&lt;/th&gt;&lt;th style="padding:10px; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height-alt:1.063em; color:#000000;"&gt;ASIN&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="padding:10px; border-top:2px solid #868D95; border-right:2px solid #868D95; font-size:14px; letter-spacing:none; line-height:1.2; text-align:center; mso-line-height</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>最大化您的 Prime Day 业绩</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>最大化您的 Prime Day 业绩
+尊敬的卖家，
+为 2026 年 Prime Day做好准备 - 为数百万 Prime 会员打造不容错过的优惠！加入我们今年6月为期4天活动。通过提交促销，确保充足库存，提升曝光度以助力您冲刺最佳业绩！
+如果您在 2026 年 4 月 30 日前提报秒杀或 Z 划算，您将获得每笔固定预付费 30% 的折扣。
+关键日期
+活动日期： 2026年6月 (具体日期待公布)
+提报截止日期： 促销 – 2026 年 6 月 19 日，价格折扣 – 活动结束前 12 小时
+FBA入仓截止日期：
+欧盟 – 2026年5月27日，英国 – 2026年6月5日
+提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D436798875-Wk18/7z351cx/6634608921/h/wJh8FOptIJNxQjFcUNHXJOBSSiJAYJe5bu6P0nX78jo
+&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="section" role="presentation" style="width:100%;"&gt;
+	&lt;tbody&gt;
+		&lt;tr&gt;
+			&lt;td align="center"&gt;
+			&lt;div role="none"&gt;
+&lt;!--[if(mso)|(IE)]&gt;
+&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="block-grid-outlook" style="width:600px;" width="600" &gt;
+&lt;tr&gt;
+&lt;td style="line-height:0px;font-size:0px;mso-line-height-rule:exactly;"&gt;&lt;![endif]--&gt;
+			&lt;div style="margin:0 auto;border-radius:0px;max-width:600px;"&gt;
+			&lt;table align="center" border="0" cellpadding="0" cellspacing="0" role="presentation" style="width:100%;border-radius:0px;"&gt;
+				&lt;tbody&gt;
+					&lt;tr&gt;
+						&lt;td class="block-grid" style="border-radius:0px;font-size:0px;padding:12px 0px 12px 0px;text-align:center;vertical-ali</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -673,39 +831,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -720,39 +878,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -772,39 +930,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 17:03:06 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -824,39 +982,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:56 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -873,39 +1031,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 14:08:50 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -925,39 +1083,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 05:12:21 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;seller-notification@amazon.ie&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Outstanding balance on your Amazon account</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Hello,
  You have an outstanding balance on your account in the amount of 7,79 EUR. We will debit this amount from the credit card (Visa) that you registered as the charge method for your account.
@@ -971,39 +1129,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:13:11 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1019,39 +1177,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:52:19 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1070,39 +1228,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 03:13:33 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20093870001] Other account issues</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Hello from Amazon Selling Partner Support,
 My name is Ritam. I am a Live Channel Specialist and I'm contacting you to follow up on your concern regarding the reinstatement of your listing B0FCDRNTT8.
@@ -1113,39 +1271,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Apr 2026 17:15:23 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -1164,141 +1322,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact on your account, close or delete any non-compliant listings that you</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -1327,40 +1383,40 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -1373,39 +1429,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -1420,39 +1476,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -1465,40 +1521,40 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -1513,40 +1569,40 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -1560,39 +1616,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -1606,39 +1662,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -1653,39 +1709,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -1699,39 +1755,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -1746,39 +1802,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1793,39 +1849,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -1844,39 +1900,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1892,39 +1948,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1945,60 +2001,10 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hola, Weihai EU:
- Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
--
- Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
- Para v</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2013,272 +2019,21 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
+          <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
- productvermelding te voorkomen</t>
+          <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hallo Weihai EU,
- Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
--
- Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
- Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
--
- Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
--
- Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hej Weihai EU!
- Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
--
- Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
- Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
- disattivazione dell'offerta</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>96
- Gentile Weihai EU,
- Alcune delle tue offerte sono a rischio di disattivazione perché i relativi prodotti non soddisfano i requisiti obbligatori sulla conformità. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i documenti di conformità.
--
- Se ritieni che i tuoi prodotti siano esenti da questi requisiti, invia la documentazione che dimostra il motivo per cui non sono soggetti a questi requisiti di conformità.
- Per istruzioni dettagliate, consulta l</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>96
- Bonjour Weihai EU,
- Certaines de vos mises en vente risquent d’être désactivées, car vos produits ne respectent pas les exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructions pour soumettre vos documents de conformité.
--
- Si vous pensez que vos produits sont exemptés de ces exigences, soumettez des pièces justificatives prouvant les raisons pour lesquelles ils ne sont pas soumis à ces exigences de conformité.
- Pour des instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2302,39 +2057,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2355,39 +2110,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -2436,39 +2191,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2484,39 +2239,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2536,39 +2291,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2594,39 +2349,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2647,39 +2402,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2705,91 +2460,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (CQhO1/+c38)</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-5850124-1743211
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-650912521107592</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 15:01:26 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2809,39 +2512,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 14:27:43 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2858,39 +2561,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2906,39 +2609,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2958,39 +2661,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3007,39 +2710,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3051,39 +2754,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3106,39 +2809,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3162,39 +2865,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3209,39 +2912,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3255,40 +2958,40 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3305,39 +3008,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3357,39 +3060,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3406,94 +3109,141 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amazon Services
- 96
- Review details about your EPR Pay on Behalf reserved amount
- Hello,
- Starting 01-04-2026, we'll hold €501.64 from your payments to cover the eco-contribution fees and Extended Producer Responsibility (EPR) Pay on Behalf service fees for sales of products subject to EPR obligations in our Amazon.es - Amazon.fr store in 2025.
- EPR Pay on Behalf calculates and pays eco-contribution fees for your sales, then debits those amounts from your account. Once fees are charged, any excess reserves will return to your account.
- Our records show you have products listed in the following EPR categories:
- - Do-it-yourself (DIY)
- - Electronical and electrical equipment
- - Packaging
- - Sports
- - Textile
- - Toys
- The amount held back is a combination of two fees:
- Due eco-contribution fees - €299.7
- EPR Pay on Behalf service fees - €201.94
- After 01-04-2026, to review your ASIN-level calculations, reserved amount details, and the reporting period for each EPR category, go to the EPR Pay on Behalf dashboard .
- The reserved amount will be adjusted monthly according to your sales volume. If the reserved amount isn't enough to cover the eco-contributions, we'll charge the additional </t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:15:37 +0000</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:09:18 +0000</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai EU,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact on your account, close or delete any non-compliant listings that you</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 03:03:00 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -3513,39 +3263,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 01:27:00 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20061337331] 对危险品分类提出异议</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商:您好!
 我们了解到您希望重新激活商品 ASIN: B0FCDRNTT8。
@@ -3574,39 +3324,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 10:07:05 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -3624,39 +3374,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:15:48 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3674,39 +3424,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:08:57 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3724,39 +3474,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 06:10:23 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12449434352] 【邀请函】诚邀您参与亚马逊卖家合规策略调研</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴，
 您好！
@@ -3770,39 +3520,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3820,40 +3570,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3870,40 +3620,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -3920,39 +3670,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -3986,39 +3736,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 10:14:18 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -4033,39 +3783,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 03:38:27 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -4081,39 +3831,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
@@ -4137,39 +3887,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -4188,39 +3938,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 09:10:03 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -4236,39 +3986,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 07:35:31 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Seller Assistant now available in the UK
 [Amazon logo](https://go.amazonsellerservices.com/e/229492/-ld-EMUSSMX-PD25/7z2r9lq/6605548725/h/3xRPn8Yyq31Jz0Gqi8FK51O58vBJkaDT5nhLB1ousbA)
@@ -4280,39 +4030,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 06:23:28 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -4332,39 +4082,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Apr 2026 09:09:25 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4382,40 +4132,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 15:28:03 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -4433,39 +4183,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 12:03:53 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -4485,39 +4235,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:50:30 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4538,39 +4288,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:38:53 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>EU and UK Compliance Brief</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe
  96
@@ -4591,40 +4341,40 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 10:23:33 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>The Amazon Europe team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>VAT Calculation Services will calculate VAT by shipment as of June
  1</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  New tax calculation method ensures compliance with European e-invoicing mandates.
@@ -4640,39 +4390,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -4695,39 +4445,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4745,39 +4495,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4795,39 +4545,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -4847,6 +4597,257 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hola, Weihai EU:
+ Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
+ ¿A qué se debe esto?
+ Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
+ En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
+ ¿Cómo puedo reactivar mis listings?
+ Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
+-
+ Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
+-
+ Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
+ Para v</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
+ productvermelding te voorkomen</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hallo Weihai EU,
+ Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
+ Waarom gebeurt dit?
+ We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
+ De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
+ Hoe activeer ik mijn productvermeldingen opnieuw?
+ Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
+-
+ Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
+-
+ Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
+ Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
+-
+ Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
+-
+ Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hej Weihai EU!
+ Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
+-
+ Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
+ Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
+ disattivazione dell'offerta</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono a rischio di disattivazione perché i relativi prodotti non soddisfano i requisiti obbligatori sulla conformità. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i documenti di conformità.
+-
+ Se ritieni che i tuoi prodotti siano esenti da questi requisiti, invia la documentazione che dimostra il motivo per cui non sono soggetti a questi requisiti di conformità.
+ Per istruzioni dettagliate, consulta l</t>
+        </is>
+      </c>
+    </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
@@ -4865,21 +4866,71 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
+          <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>规划您的 La French Week 促销活动</t>
+          <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente risquent d’être désactivées, car vos produits ne respectent pas les exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructions pour soumettre vos documents de conformité.
+-
+ Si vous pensez que vos produits sont exemptés de ces exigences, soumettez des pièces justificatives prouvant les raisons pour lesquelles ils ne sont pas soumis à ces exigences de conformité.
+ Pour des instru</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>规划您的 La French Week 促销活动</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4896,39 +4947,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4943,39 +4994,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4994,39 +5045,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -5044,39 +5095,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -5115,39 +5166,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -5163,40 +5214,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -5212,39 +5263,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -5260,39 +5311,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -5306,40 +5357,40 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -5355,39 +5406,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -5403,39 +5454,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5456,39 +5507,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5503,39 +5554,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -5552,39 +5603,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5598,39 +5649,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -5649,40 +5700,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -5696,40 +5747,40 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -5747,39 +5798,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -5812,39 +5863,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -5859,39 +5910,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5910,39 +5961,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -5961,39 +6012,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -6005,39 +6056,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -6053,39 +6104,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -6097,39 +6148,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6144,39 +6195,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6188,39 +6239,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6232,39 +6283,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6276,39 +6327,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6320,39 +6371,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6364,39 +6415,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6408,39 +6459,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6452,39 +6503,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6496,39 +6547,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6540,39 +6591,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6591,39 +6642,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6635,39 +6686,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6679,39 +6730,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6723,39 +6774,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6767,39 +6818,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6811,39 +6862,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6855,39 +6906,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6899,39 +6950,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6950,39 +7001,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6994,40 +7045,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -7046,39 +7097,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -7090,39 +7141,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -7141,39 +7192,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -7205,39 +7256,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -7264,39 +7315,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -7308,39 +7359,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -7350,39 +7401,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -7392,39 +7443,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -7454,39 +7505,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7504,39 +7555,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7553,58 +7604,10 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
-        </is>
-      </c>
-      <c r="E144" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
-        </is>
-      </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
-Dear there,
-Thank you again for being a valued member of the Amazon Multichannel Fulfillment (MCF) and Buy with Prime community. We are reaching again out to make sure you have seen that starting in April 2026, MCF and Buy with Prime will introduce two updates to how orders are packaged and shipped in the United States:
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-https://www2.amazonsupplychain.com/e/949422/ence-external-GVCFXDFYNCTFLTTQ/61cb1y/1376709412/h/1WNFlb9vThQHSQY7UXRXBztlSOEepEEyvW_3PEnZTWk
-Packing slips will no longer be included by default.
-Items already certified for the Ships in Product Packaging (SIPP) program on Amazon.com will ship without an Amazon overbox by default.
-In addition, eligible MCF and Buy with Prime SIPP shipments will receive a discount. See the SIPP for MCF help content for details.
-These updates support Amazon</t>
-        </is>
-      </c>
-    </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7619,82 +7622,21 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
+          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Tus límites de capacidad de Logística de Amazon para abril</t>
+          <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>96
- Tus límites de capacidad de Logística de Amazon para abril
- Hola:
- Se confirmaron tus límites de capacidad para el próximo periodo.
- Pronóstico de capacidad para el periodo del abr. 1 al 30, a partir del mar. 28:
- Tipo de almacenamiento
- Límite de capacidad total (metros cúbicos)
- Tamaño estándar
- 16.42
- Tamaño grande
- 21.66
- Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
- En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del mar. 27.
- Tipo de almacenamiento
- Uso sin los envíos abiertos incluidos (metros cúbicos)
- Uso con los envíos abiertos incluidos (metros cúbicos)
- Tamaño estándar
- 0.00
- 0.00
- Tamaño grande
- 0.00
- 0.00
- Cómo se establecen los límites de capacidad de Logística de Amazon
- Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
-        </is>
-      </c>
-      <c r="E146" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-30</t>
-        </is>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7716,39 +7658,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7771,39 +7713,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7824,39 +7766,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7879,39 +7821,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -7924,39 +7866,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -7965,39 +7907,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -8013,39 +7955,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -8061,39 +8003,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -8113,39 +8055,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -8164,39 +8106,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -8205,39 +8147,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -8255,39 +8197,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
